--- a/downloads/loesungen/07_Schule_3NF_Loesung.xlsx
+++ b/downloads/loesungen/07_Schule_3NF_Loesung.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER" sheetId="1" r:id="R971a99f55a674b22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KLASSE" sheetId="2" r:id="R08ca75ba05614849"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNTERRICHT" sheetId="3" r:id="Ra54b3e1f4524486d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER_UNTERRICHT" sheetId="4" r:id="R61f15a24d5874384"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER" sheetId="1" r:id="R1344e6b0c80d4a08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KLASSE" sheetId="2" r:id="Red396b43a4aa48b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNTERRICHT" sheetId="3" r:id="Ra5df37a04df7436b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER_UNTERRICHT" sheetId="4" r:id="R7e0129f76e7f45ae"/>
   </x:sheets>
 </x:workbook>
 </file>
